--- a/data/trans_orig/P57B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat) en 2023</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) en 2023 (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95563</t>
+          <t>95868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128283</t>
+          <t>130561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>199940</t>
+          <t>200094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238163</t>
+          <t>234050</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>305933</t>
+          <t>307481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>354024</t>
+          <t>355766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372528</t>
+          <t>370250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405248</t>
+          <t>404943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>487701</t>
+          <t>491814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>525770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>872650</t>
+          <t>870908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>920741</t>
+          <t>919193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117993</t>
+          <t>117961</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202099</t>
+          <t>202338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147610</t>
+          <t>156384</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246259</t>
+          <t>246458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>303094</t>
+          <t>296380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>432420</t>
+          <t>437106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2063137</t>
+          <t>2062898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2147243</t>
+          <t>2147275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1968455</t>
+          <t>1968256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2067104</t>
+          <t>2058330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4047530</t>
+          <t>4042844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4176856</t>
+          <t>4183570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>28766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56296</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,47 +1431,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>57520</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>46477</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>71761</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>8,76%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>57520</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>46443</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>70647</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81461</t>
+          <t>82086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115754</t>
+          <t>118774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>586281</t>
+          <t>585555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613891</t>
+          <t>613811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,47 +1544,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>91,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>599366</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>585125</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>610409</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>91,24%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>599366</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>586239</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>610443</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,24%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1183710</t>
+          <t>1180690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1218003</t>
+          <t>1217378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252816</t>
+          <t>251946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>362640</t>
+          <t>364659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>404852</t>
+          <t>395905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>538177</t>
+          <t>534862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>695377</t>
+          <t>695907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>874319</t>
+          <t>879267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3045985</t>
+          <t>3043966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3155809</t>
+          <t>3156679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3059286</t>
+          <t>3062601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3192611</t>
+          <t>3201558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6131769</t>
+          <t>6126821</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6310711</t>
+          <t>6310181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/P57B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>111707</t>
+          <t>122305</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95868</t>
+          <t>104379</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130561</t>
+          <t>140384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>217768</t>
+          <t>238412</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200094</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234050</t>
+          <t>258202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>329475</t>
+          <t>360717</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>307481</t>
+          <t>334663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>355766</t>
+          <t>387313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>389104</t>
+          <t>436328</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>370250</t>
+          <t>418249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404943</t>
+          <t>454254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>508096</t>
+          <t>551592</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>491814</t>
+          <t>531802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>525770</t>
+          <t>572450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>897199</t>
+          <t>987920</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870908</t>
+          <t>961324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>919193</t>
+          <t>1013974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>500811</t>
+          <t>558633</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>500811</t>
+          <t>558633</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>500811</t>
+          <t>558633</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725864</t>
+          <t>790004</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725864</t>
+          <t>790004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725864</t>
+          <t>790004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1226674</t>
+          <t>1348637</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1226674</t>
+          <t>1348637</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1226674</t>
+          <t>1348637</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>170209</t>
+          <t>187335</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117961</t>
+          <t>162492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202338</t>
+          <t>215436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>211102</t>
+          <t>239726</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156384</t>
+          <t>215164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246458</t>
+          <t>265172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>381311</t>
+          <t>427060</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>296380</t>
+          <t>392550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>437106</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2095027</t>
+          <t>2018040</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2062898</t>
+          <t>1989939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2147275</t>
+          <t>2042883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2003612</t>
+          <t>1904605</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1968256</t>
+          <t>1879159</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2058330</t>
+          <t>1929167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4098639</t>
+          <t>3922645</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4042844</t>
+          <t>3885791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4183570</t>
+          <t>3957155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2265236</t>
+          <t>2205375</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2265236</t>
+          <t>2205375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2265236</t>
+          <t>2205375</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2214714</t>
+          <t>2144331</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2214714</t>
+          <t>2144331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2214714</t>
+          <t>2144331</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4479950</t>
+          <t>4349705</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4479950</t>
+          <t>4349705</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4479950</t>
+          <t>4349705</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40527</t>
+          <t>44978</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28766</t>
+          <t>33506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57022</t>
+          <t>61566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57520</t>
+          <t>62186</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46477</t>
+          <t>49766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>76747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>98047</t>
+          <t>107165</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82086</t>
+          <t>87493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118774</t>
+          <t>127306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>602050</t>
+          <t>662435</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>585555</t>
+          <t>645847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613811</t>
+          <t>673907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>599366</t>
+          <t>668590</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>585125</t>
+          <t>654029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>610409</t>
+          <t>681010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1201417</t>
+          <t>1331024</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1180690</t>
+          <t>1310883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1217378</t>
+          <t>1350696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>642577</t>
+          <t>707413</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>642577</t>
+          <t>707413</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>642577</t>
+          <t>707413</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>656886</t>
+          <t>730776</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>656886</t>
+          <t>730776</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>656886</t>
+          <t>730776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1299464</t>
+          <t>1438189</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1299464</t>
+          <t>1438189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1299464</t>
+          <t>1438189</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>322443</t>
+          <t>354618</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>251946</t>
+          <t>320755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>364659</t>
+          <t>390738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>486390</t>
+          <t>540324</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>395905</t>
+          <t>506880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>534862</t>
+          <t>576044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>808833</t>
+          <t>894942</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>695907</t>
+          <t>845743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>879267</t>
+          <t>946919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3086182</t>
+          <t>3116803</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3043966</t>
+          <t>3080683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3156679</t>
+          <t>3150666</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3111073</t>
+          <t>3124786</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3062601</t>
+          <t>3089066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3201558</t>
+          <t>3158230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6197255</t>
+          <t>6241590</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6126821</t>
+          <t>6189613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6310181</t>
+          <t>6290789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3408625</t>
+          <t>3471421</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3408625</t>
+          <t>3471421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3408625</t>
+          <t>3471421</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3597463</t>
+          <t>3665110</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3597463</t>
+          <t>3665110</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3597463</t>
+          <t>3665110</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7006088</t>
+          <t>7136532</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7006088</t>
+          <t>7136532</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7006088</t>
+          <t>7136532</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
